--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_o_higgins.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,28 +408,28 @@
         </is>
       </c>
       <c r="B2">
+        <v>53.80188</v>
+      </c>
+      <c r="C2">
+        <v>95.24541000000001</v>
+      </c>
+      <c r="D2">
+        <v>81.92401</v>
+      </c>
+      <c r="E2">
+        <v>42.27129</v>
+      </c>
+      <c r="F2">
         <v>54.27809</v>
       </c>
-      <c r="C2">
-        <v>53.80188</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>100.543</v>
       </c>
-      <c r="E2">
-        <v>95.24541000000001</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>102.4497</v>
       </c>
-      <c r="G2">
-        <v>81.92401</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>64.72678000000001</v>
-      </c>
-      <c r="I2">
-        <v>42.27129</v>
       </c>
     </row>
     <row r="3">
@@ -439,28 +439,28 @@
         </is>
       </c>
       <c r="B3">
+        <v>58.41584</v>
+      </c>
+      <c r="C3">
+        <v>95.75924000000001</v>
+      </c>
+      <c r="D3">
+        <v>84.31912</v>
+      </c>
+      <c r="E3">
+        <v>38.69132</v>
+      </c>
+      <c r="F3">
         <v>58.52585</v>
       </c>
-      <c r="C3">
-        <v>58.41584</v>
-      </c>
-      <c r="D3">
+      <c r="G3">
         <v>100.8892</v>
       </c>
-      <c r="E3">
-        <v>95.75924000000001</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>105.227</v>
       </c>
-      <c r="G3">
-        <v>84.31912</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>55.19204</v>
-      </c>
-      <c r="I3">
-        <v>38.69132</v>
       </c>
     </row>
     <row r="4">
@@ -470,28 +470,28 @@
         </is>
       </c>
       <c r="B4">
+        <v>53.26316</v>
+      </c>
+      <c r="C4">
+        <v>96.2963</v>
+      </c>
+      <c r="D4">
+        <v>86.19855</v>
+      </c>
+      <c r="E4">
+        <v>43.97436</v>
+      </c>
+      <c r="F4">
         <v>53.47368</v>
       </c>
-      <c r="C4">
-        <v>53.26316</v>
-      </c>
-      <c r="D4">
+      <c r="G4">
         <v>100.6386</v>
       </c>
-      <c r="E4">
-        <v>96.2963</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>101.6949</v>
       </c>
-      <c r="G4">
-        <v>86.19855</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>56.92308</v>
-      </c>
-      <c r="I4">
-        <v>43.97436</v>
       </c>
     </row>
     <row r="5">
@@ -501,28 +501,28 @@
         </is>
       </c>
       <c r="B5">
+        <v>53.76712</v>
+      </c>
+      <c r="C5">
+        <v>96.52997000000001</v>
+      </c>
+      <c r="D5">
+        <v>83.68794</v>
+      </c>
+      <c r="E5">
+        <v>34.81319</v>
+      </c>
+      <c r="F5">
         <v>54.45205</v>
       </c>
-      <c r="C5">
-        <v>53.76712</v>
-      </c>
-      <c r="D5">
+      <c r="G5">
         <v>102.6138</v>
       </c>
-      <c r="E5">
-        <v>96.52997000000001</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>106.2057</v>
       </c>
-      <c r="G5">
-        <v>83.68794</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>45.75824</v>
-      </c>
-      <c r="I5">
-        <v>34.81319</v>
       </c>
     </row>
     <row r="6">
@@ -532,28 +532,28 @@
         </is>
       </c>
       <c r="B6">
+        <v>58.58407</v>
+      </c>
+      <c r="C6">
+        <v>96.83841</v>
+      </c>
+      <c r="D6">
+        <v>84.75512999999999</v>
+      </c>
+      <c r="E6">
+        <v>40.70103</v>
+      </c>
+      <c r="F6">
         <v>59.17404</v>
       </c>
-      <c r="C6">
-        <v>58.58407</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
         <v>101.8735</v>
       </c>
-      <c r="E6">
-        <v>96.83841</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>101.0269</v>
       </c>
-      <c r="G6">
-        <v>84.75512999999999</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>56.24742</v>
-      </c>
-      <c r="I6">
-        <v>40.70103</v>
       </c>
     </row>
     <row r="7">
@@ -563,28 +563,28 @@
         </is>
       </c>
       <c r="B7">
+        <v>53.0492</v>
+      </c>
+      <c r="C7">
+        <v>95.79671999999999</v>
+      </c>
+      <c r="D7">
+        <v>81.50317</v>
+      </c>
+      <c r="E7">
+        <v>36.90727</v>
+      </c>
+      <c r="F7">
         <v>53.43036</v>
       </c>
-      <c r="C7">
-        <v>53.0492</v>
-      </c>
-      <c r="D7">
+      <c r="G7">
         <v>101.2824</v>
       </c>
-      <c r="E7">
-        <v>95.79671999999999</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>104.246</v>
       </c>
-      <c r="G7">
-        <v>81.50317</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>53.50369</v>
-      </c>
-      <c r="I7">
-        <v>36.90727</v>
       </c>
     </row>
     <row r="8">
@@ -594,28 +594,28 @@
         </is>
       </c>
       <c r="B8">
+        <v>57.8887</v>
+      </c>
+      <c r="C8">
+        <v>97.06194000000001</v>
+      </c>
+      <c r="D8">
+        <v>85.98999000000001</v>
+      </c>
+      <c r="E8">
+        <v>33.23101</v>
+      </c>
+      <c r="F8">
         <v>58.11819</v>
       </c>
-      <c r="C8">
-        <v>57.8887</v>
-      </c>
-      <c r="D8">
+      <c r="G8">
         <v>102.3009</v>
       </c>
-      <c r="E8">
-        <v>97.06194000000001</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>103.5025</v>
       </c>
-      <c r="G8">
-        <v>85.98999000000001</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
         <v>42.70913</v>
-      </c>
-      <c r="I8">
-        <v>33.23101</v>
       </c>
     </row>
     <row r="9">
@@ -625,28 +625,28 @@
         </is>
       </c>
       <c r="B9">
+        <v>46.41603</v>
+      </c>
+      <c r="C9">
+        <v>94.9705</v>
+      </c>
+      <c r="D9">
+        <v>84.83619</v>
+      </c>
+      <c r="E9">
+        <v>51.29844</v>
+      </c>
+      <c r="F9">
         <v>47.15968</v>
       </c>
-      <c r="C9">
-        <v>46.41603</v>
-      </c>
-      <c r="D9">
+      <c r="G9">
         <v>99.14455</v>
       </c>
-      <c r="E9">
-        <v>94.9705</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>101.7161</v>
       </c>
-      <c r="G9">
-        <v>84.83619</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>73.11227</v>
-      </c>
-      <c r="I9">
-        <v>51.29844</v>
       </c>
     </row>
     <row r="10">
@@ -656,28 +656,28 @@
         </is>
       </c>
       <c r="B10">
+        <v>56.97808</v>
+      </c>
+      <c r="C10">
+        <v>96.75994</v>
+      </c>
+      <c r="D10">
+        <v>83.2664</v>
+      </c>
+      <c r="E10">
+        <v>32.15979</v>
+      </c>
+      <c r="F10">
         <v>57.3241</v>
       </c>
-      <c r="C10">
-        <v>56.97808</v>
-      </c>
-      <c r="D10">
+      <c r="G10">
         <v>101.7673</v>
       </c>
-      <c r="E10">
-        <v>96.75994</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>96.11781000000001</v>
       </c>
-      <c r="G10">
-        <v>83.2664</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>44.00813</v>
-      </c>
-      <c r="I10">
-        <v>32.15979</v>
       </c>
     </row>
     <row r="11">
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="B11">
+        <v>56.49414</v>
+      </c>
+      <c r="C11">
+        <v>95.91567999999999</v>
+      </c>
+      <c r="D11">
+        <v>81.20977999999999</v>
+      </c>
+      <c r="E11">
+        <v>35.09084</v>
+      </c>
+      <c r="F11">
         <v>56.64063</v>
       </c>
-      <c r="C11">
-        <v>56.49414</v>
-      </c>
-      <c r="D11">
+      <c r="G11">
         <v>102.5033</v>
       </c>
-      <c r="E11">
-        <v>95.91567999999999</v>
-      </c>
-      <c r="F11">
+      <c r="H11">
         <v>105.6628</v>
       </c>
-      <c r="G11">
-        <v>81.20977999999999</v>
-      </c>
-      <c r="H11">
+      <c r="I11">
         <v>49.59031</v>
-      </c>
-      <c r="I11">
-        <v>35.09084</v>
       </c>
     </row>
     <row r="12">
@@ -718,28 +718,28 @@
         </is>
       </c>
       <c r="B12">
+        <v>54.13892</v>
+      </c>
+      <c r="C12">
+        <v>96.40758</v>
+      </c>
+      <c r="D12">
+        <v>82.54546000000001</v>
+      </c>
+      <c r="E12">
+        <v>42.08417</v>
+      </c>
+      <c r="F12">
         <v>54.5195</v>
       </c>
-      <c r="C12">
-        <v>54.13892</v>
-      </c>
-      <c r="D12">
+      <c r="G12">
         <v>100.8491</v>
       </c>
-      <c r="E12">
-        <v>96.40758</v>
-      </c>
-      <c r="F12">
+      <c r="H12">
         <v>103.1515</v>
       </c>
-      <c r="G12">
-        <v>82.54546000000001</v>
-      </c>
-      <c r="H12">
+      <c r="I12">
         <v>56.11222</v>
-      </c>
-      <c r="I12">
-        <v>42.08417</v>
       </c>
     </row>
     <row r="13">
@@ -749,28 +749,28 @@
         </is>
       </c>
       <c r="B13">
+        <v>61.74863</v>
+      </c>
+      <c r="C13">
+        <v>96.87084</v>
+      </c>
+      <c r="D13">
+        <v>82.8125</v>
+      </c>
+      <c r="E13">
+        <v>35.3826</v>
+      </c>
+      <c r="F13">
         <v>62.40437</v>
       </c>
-      <c r="C13">
-        <v>61.74863</v>
-      </c>
-      <c r="D13">
+      <c r="G13">
         <v>102.1305</v>
       </c>
-      <c r="E13">
-        <v>96.87084</v>
-      </c>
-      <c r="F13">
+      <c r="H13">
         <v>107.4219</v>
       </c>
-      <c r="G13">
-        <v>82.8125</v>
-      </c>
-      <c r="H13">
+      <c r="I13">
         <v>50.16351</v>
-      </c>
-      <c r="I13">
-        <v>35.3826</v>
       </c>
     </row>
     <row r="14">
@@ -780,28 +780,28 @@
         </is>
       </c>
       <c r="B14">
+        <v>56.87398</v>
+      </c>
+      <c r="C14">
+        <v>97.20386999999999</v>
+      </c>
+      <c r="D14">
+        <v>87.74194</v>
+      </c>
+      <c r="E14">
+        <v>35.31998</v>
+      </c>
+      <c r="F14">
         <v>57.03764</v>
       </c>
-      <c r="C14">
-        <v>56.87398</v>
-      </c>
-      <c r="D14">
+      <c r="G14">
         <v>101.9319</v>
       </c>
-      <c r="E14">
-        <v>97.20386999999999</v>
-      </c>
-      <c r="F14">
+      <c r="H14">
         <v>98.70968000000001</v>
       </c>
-      <c r="G14">
-        <v>87.74194</v>
-      </c>
-      <c r="H14">
+      <c r="I14">
         <v>44.94382</v>
-      </c>
-      <c r="I14">
-        <v>35.31998</v>
       </c>
     </row>
     <row r="15">
@@ -811,28 +811,28 @@
         </is>
       </c>
       <c r="B15">
+        <v>56.95509</v>
+      </c>
+      <c r="C15">
+        <v>96.78342000000001</v>
+      </c>
+      <c r="D15">
+        <v>86.41304</v>
+      </c>
+      <c r="E15">
+        <v>41.82825</v>
+      </c>
+      <c r="F15">
         <v>57.06462</v>
       </c>
-      <c r="C15">
-        <v>56.95509</v>
-      </c>
-      <c r="D15">
+      <c r="G15">
         <v>100.5718</v>
       </c>
-      <c r="E15">
-        <v>96.78342000000001</v>
-      </c>
-      <c r="F15">
+      <c r="H15">
         <v>103.3967</v>
       </c>
-      <c r="G15">
-        <v>86.41304</v>
-      </c>
-      <c r="H15">
+      <c r="I15">
         <v>56.5097</v>
-      </c>
-      <c r="I15">
-        <v>41.82825</v>
       </c>
     </row>
     <row r="16">
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="B16">
+        <v>56.71073</v>
+      </c>
+      <c r="C16">
+        <v>95.84076</v>
+      </c>
+      <c r="D16">
+        <v>84.09026</v>
+      </c>
+      <c r="E16">
+        <v>37.47709</v>
+      </c>
+      <c r="F16">
         <v>57.02442</v>
       </c>
-      <c r="C16">
-        <v>56.71073</v>
-      </c>
-      <c r="D16">
+      <c r="G16">
         <v>101.4409</v>
       </c>
-      <c r="E16">
-        <v>95.84076</v>
-      </c>
-      <c r="F16">
+      <c r="H16">
         <v>106.0554</v>
       </c>
-      <c r="G16">
-        <v>84.09026</v>
-      </c>
-      <c r="H16">
+      <c r="I16">
         <v>54.4441</v>
-      </c>
-      <c r="I16">
-        <v>37.47709</v>
       </c>
     </row>
     <row r="17">
@@ -873,28 +873,28 @@
         </is>
       </c>
       <c r="B17">
+        <v>57.18954</v>
+      </c>
+      <c r="C17">
+        <v>96.58808999999999</v>
+      </c>
+      <c r="D17">
+        <v>84.14122999999999</v>
+      </c>
+      <c r="E17">
+        <v>39.2151</v>
+      </c>
+      <c r="F17">
         <v>57.93651</v>
       </c>
-      <c r="C17">
-        <v>57.18954</v>
-      </c>
-      <c r="D17">
+      <c r="G17">
         <v>101.5819</v>
       </c>
-      <c r="E17">
-        <v>96.58808999999999</v>
-      </c>
-      <c r="F17">
+      <c r="H17">
         <v>100.1795</v>
       </c>
-      <c r="G17">
-        <v>84.14122999999999</v>
-      </c>
-      <c r="H17">
+      <c r="I17">
         <v>51.46795</v>
-      </c>
-      <c r="I17">
-        <v>39.2151</v>
       </c>
     </row>
     <row r="18">
@@ -904,28 +904,28 @@
         </is>
       </c>
       <c r="B18">
+        <v>59.91272</v>
+      </c>
+      <c r="C18">
+        <v>97.13283</v>
+      </c>
+      <c r="D18">
+        <v>84.88549999999999</v>
+      </c>
+      <c r="E18">
+        <v>41.0626</v>
+      </c>
+      <c r="F18">
         <v>60.31796</v>
       </c>
-      <c r="C18">
-        <v>59.91272</v>
-      </c>
-      <c r="D18">
+      <c r="G18">
         <v>101.7749</v>
       </c>
-      <c r="E18">
-        <v>97.13283</v>
-      </c>
-      <c r="F18">
+      <c r="H18">
         <v>100.3817</v>
       </c>
-      <c r="G18">
-        <v>84.88549999999999</v>
-      </c>
-      <c r="H18">
+      <c r="I18">
         <v>55.45716</v>
-      </c>
-      <c r="I18">
-        <v>41.0626</v>
       </c>
     </row>
     <row r="19">
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="B19">
+        <v>50.31898</v>
+      </c>
+      <c r="C19">
+        <v>93.5132</v>
+      </c>
+      <c r="D19">
+        <v>84.43774999999999</v>
+      </c>
+      <c r="E19">
+        <v>38.39526</v>
+      </c>
+      <c r="F19">
         <v>50.63796</v>
       </c>
-      <c r="C19">
-        <v>50.31898</v>
-      </c>
-      <c r="D19">
+      <c r="G19">
         <v>97.35936</v>
       </c>
-      <c r="E19">
-        <v>93.5132</v>
-      </c>
-      <c r="F19">
+      <c r="H19">
         <v>100.4016</v>
       </c>
-      <c r="G19">
-        <v>84.43774999999999</v>
-      </c>
-      <c r="H19">
+      <c r="I19">
         <v>50.99623</v>
-      </c>
-      <c r="I19">
-        <v>38.39526</v>
       </c>
     </row>
     <row r="20">
@@ -969,25 +969,25 @@
         <v>56.6879</v>
       </c>
       <c r="C20">
+        <v>96.91781</v>
+      </c>
+      <c r="D20">
+        <v>87.19512</v>
+      </c>
+      <c r="E20">
+        <v>40.22556</v>
+      </c>
+      <c r="F20">
         <v>56.6879</v>
       </c>
-      <c r="D20">
+      <c r="G20">
         <v>103.0822</v>
       </c>
-      <c r="E20">
-        <v>96.91781</v>
-      </c>
-      <c r="F20">
+      <c r="H20">
         <v>101.8293</v>
       </c>
-      <c r="G20">
-        <v>87.19512</v>
-      </c>
-      <c r="H20">
+      <c r="I20">
         <v>58.27068</v>
-      </c>
-      <c r="I20">
-        <v>40.22556</v>
       </c>
     </row>
     <row r="21">
@@ -997,28 +997,28 @@
         </is>
       </c>
       <c r="B21">
+        <v>51.50812</v>
+      </c>
+      <c r="C21">
+        <v>95.50897999999999</v>
+      </c>
+      <c r="D21">
+        <v>79.58580000000001</v>
+      </c>
+      <c r="E21">
+        <v>37.9021</v>
+      </c>
+      <c r="F21">
         <v>51.74014</v>
       </c>
-      <c r="C21">
-        <v>51.50812</v>
-      </c>
-      <c r="D21">
+      <c r="G21">
         <v>102.0958</v>
       </c>
-      <c r="E21">
-        <v>95.50897999999999</v>
-      </c>
-      <c r="F21">
+      <c r="H21">
         <v>99.11243</v>
       </c>
-      <c r="G21">
-        <v>79.58580000000001</v>
-      </c>
-      <c r="H21">
+      <c r="I21">
         <v>50.34965</v>
-      </c>
-      <c r="I21">
-        <v>37.9021</v>
       </c>
     </row>
     <row r="22">
@@ -1028,28 +1028,28 @@
         </is>
       </c>
       <c r="B22">
+        <v>62.9717</v>
+      </c>
+      <c r="C22">
+        <v>95.94595</v>
+      </c>
+      <c r="D22">
+        <v>86.31091000000001</v>
+      </c>
+      <c r="E22">
+        <v>37.34533</v>
+      </c>
+      <c r="F22">
         <v>63.20755</v>
       </c>
-      <c r="C22">
-        <v>62.9717</v>
-      </c>
-      <c r="D22">
+      <c r="G22">
         <v>101.6516</v>
       </c>
-      <c r="E22">
-        <v>95.94595</v>
-      </c>
-      <c r="F22">
+      <c r="H22">
         <v>99.76797999999999</v>
       </c>
-      <c r="G22">
-        <v>86.31091000000001</v>
-      </c>
-      <c r="H22">
+      <c r="I22">
         <v>49.38133</v>
-      </c>
-      <c r="I22">
-        <v>37.34533</v>
       </c>
     </row>
     <row r="23">
@@ -1059,28 +1059,28 @@
         </is>
       </c>
       <c r="B23">
+        <v>53.35051</v>
+      </c>
+      <c r="C23">
+        <v>94.72759000000001</v>
+      </c>
+      <c r="D23">
+        <v>78.91157</v>
+      </c>
+      <c r="E23">
+        <v>31.13402</v>
+      </c>
+      <c r="F23">
         <v>53.60825</v>
       </c>
-      <c r="C23">
-        <v>53.35051</v>
-      </c>
-      <c r="D23">
+      <c r="G23">
         <v>101.2302</v>
       </c>
-      <c r="E23">
-        <v>94.72759000000001</v>
-      </c>
-      <c r="F23">
+      <c r="H23">
         <v>101.7007</v>
       </c>
-      <c r="G23">
-        <v>78.91157</v>
-      </c>
-      <c r="H23">
+      <c r="I23">
         <v>42.06186</v>
-      </c>
-      <c r="I23">
-        <v>31.13402</v>
       </c>
     </row>
     <row r="24">
@@ -1093,25 +1093,25 @@
         <v>49.68554</v>
       </c>
       <c r="C24">
+        <v>96.67283</v>
+      </c>
+      <c r="D24">
+        <v>85.85526</v>
+      </c>
+      <c r="E24">
+        <v>36.13569</v>
+      </c>
+      <c r="F24">
         <v>49.68554</v>
       </c>
-      <c r="D24">
+      <c r="G24">
         <v>102.5878</v>
       </c>
-      <c r="E24">
-        <v>96.67283</v>
-      </c>
-      <c r="F24">
+      <c r="H24">
         <v>110.8553</v>
       </c>
-      <c r="G24">
-        <v>85.85526</v>
-      </c>
-      <c r="H24">
+      <c r="I24">
         <v>42.33038</v>
-      </c>
-      <c r="I24">
-        <v>36.13569</v>
       </c>
     </row>
     <row r="25">
@@ -1121,28 +1121,28 @@
         </is>
       </c>
       <c r="B25">
+        <v>62.83906</v>
+      </c>
+      <c r="C25">
+        <v>96.19553000000001</v>
+      </c>
+      <c r="D25">
+        <v>79.82043</v>
+      </c>
+      <c r="E25">
+        <v>38.75747</v>
+      </c>
+      <c r="F25">
         <v>63.20072</v>
       </c>
-      <c r="C25">
-        <v>62.83906</v>
-      </c>
-      <c r="D25">
+      <c r="G25">
         <v>102.073</v>
       </c>
-      <c r="E25">
-        <v>96.19553000000001</v>
-      </c>
-      <c r="F25">
+      <c r="H25">
         <v>104.8934</v>
       </c>
-      <c r="G25">
-        <v>79.82043</v>
-      </c>
-      <c r="H25">
+      <c r="I25">
         <v>55.68698</v>
-      </c>
-      <c r="I25">
-        <v>38.75747</v>
       </c>
     </row>
     <row r="26">
@@ -1152,28 +1152,28 @@
         </is>
       </c>
       <c r="B26">
+        <v>57.91856</v>
+      </c>
+      <c r="C26">
+        <v>97.28192</v>
+      </c>
+      <c r="D26">
+        <v>87.42059</v>
+      </c>
+      <c r="E26">
+        <v>37.44856</v>
+      </c>
+      <c r="F26">
         <v>58.00905</v>
       </c>
-      <c r="C26">
-        <v>57.91856</v>
-      </c>
-      <c r="D26">
+      <c r="G26">
         <v>103.9191</v>
       </c>
-      <c r="E26">
-        <v>97.28192</v>
-      </c>
-      <c r="F26">
+      <c r="H26">
         <v>104.4473</v>
       </c>
-      <c r="G26">
-        <v>87.42059</v>
-      </c>
-      <c r="H26">
+      <c r="I26">
         <v>49.58848</v>
-      </c>
-      <c r="I26">
-        <v>37.44856</v>
       </c>
     </row>
     <row r="27">
@@ -1183,28 +1183,28 @@
         </is>
       </c>
       <c r="B27">
+        <v>56.14803</v>
+      </c>
+      <c r="C27">
+        <v>96.81017</v>
+      </c>
+      <c r="D27">
+        <v>85.31842</v>
+      </c>
+      <c r="E27">
+        <v>34.31864</v>
+      </c>
+      <c r="F27">
         <v>56.46637</v>
       </c>
-      <c r="C27">
-        <v>56.14803</v>
-      </c>
-      <c r="D27">
+      <c r="G27">
         <v>102.4118</v>
       </c>
-      <c r="E27">
-        <v>96.81017</v>
-      </c>
-      <c r="F27">
+      <c r="H27">
         <v>108.8965</v>
       </c>
-      <c r="G27">
-        <v>85.31842</v>
-      </c>
-      <c r="H27">
+      <c r="I27">
         <v>47.29459</v>
-      </c>
-      <c r="I27">
-        <v>34.31864</v>
       </c>
     </row>
     <row r="28">
@@ -1217,25 +1217,25 @@
         <v>57.88177</v>
       </c>
       <c r="C28">
+        <v>97.78106</v>
+      </c>
+      <c r="D28">
+        <v>86.22754</v>
+      </c>
+      <c r="E28">
+        <v>41.0606</v>
+      </c>
+      <c r="F28">
         <v>57.88177</v>
       </c>
-      <c r="D28">
+      <c r="G28">
         <v>102.8107</v>
       </c>
-      <c r="E28">
-        <v>97.78106</v>
-      </c>
-      <c r="F28">
+      <c r="H28">
         <v>101.497</v>
       </c>
-      <c r="G28">
-        <v>86.22754</v>
-      </c>
-      <c r="H28">
+      <c r="I28">
         <v>49.69697</v>
-      </c>
-      <c r="I28">
-        <v>41.0606</v>
       </c>
     </row>
     <row r="29">
@@ -1245,28 +1245,28 @@
         </is>
       </c>
       <c r="B29">
+        <v>56.42276</v>
+      </c>
+      <c r="C29">
+        <v>96.66319</v>
+      </c>
+      <c r="D29">
+        <v>85.81632</v>
+      </c>
+      <c r="E29">
+        <v>35.59047</v>
+      </c>
+      <c r="F29">
         <v>56.58537</v>
       </c>
-      <c r="C29">
-        <v>56.42276</v>
-      </c>
-      <c r="D29">
+      <c r="G29">
         <v>101.9812</v>
       </c>
-      <c r="E29">
-        <v>96.66319</v>
-      </c>
-      <c r="F29">
+      <c r="H29">
         <v>105</v>
       </c>
-      <c r="G29">
-        <v>85.81632</v>
-      </c>
-      <c r="H29">
+      <c r="I29">
         <v>47.45395</v>
-      </c>
-      <c r="I29">
-        <v>35.59047</v>
       </c>
     </row>
     <row r="30">
@@ -1276,28 +1276,28 @@
         </is>
       </c>
       <c r="B30">
+        <v>61.87846</v>
+      </c>
+      <c r="C30">
+        <v>97.2807</v>
+      </c>
+      <c r="D30">
+        <v>86.40777</v>
+      </c>
+      <c r="E30">
+        <v>32.81114</v>
+      </c>
+      <c r="F30">
         <v>62.29282</v>
       </c>
-      <c r="C30">
-        <v>61.87846</v>
-      </c>
-      <c r="D30">
+      <c r="G30">
         <v>102.4561</v>
       </c>
-      <c r="E30">
-        <v>97.2807</v>
-      </c>
-      <c r="F30">
+      <c r="H30">
         <v>103.3981</v>
       </c>
-      <c r="G30">
-        <v>86.40777</v>
-      </c>
-      <c r="H30">
+      <c r="I30">
         <v>44.90862</v>
-      </c>
-      <c r="I30">
-        <v>32.81114</v>
       </c>
     </row>
     <row r="31">
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="B31">
+        <v>62.33766</v>
+      </c>
+      <c r="C31">
+        <v>96.38129000000001</v>
+      </c>
+      <c r="D31">
+        <v>89.12071</v>
+      </c>
+      <c r="E31">
+        <v>42.17926</v>
+      </c>
+      <c r="F31">
         <v>62.46753</v>
       </c>
-      <c r="C31">
-        <v>62.33766</v>
-      </c>
-      <c r="D31">
+      <c r="G31">
         <v>101.4122</v>
       </c>
-      <c r="E31">
-        <v>96.38129000000001</v>
-      </c>
-      <c r="F31">
+      <c r="H31">
         <v>97.6155</v>
       </c>
-      <c r="G31">
-        <v>89.12071</v>
-      </c>
-      <c r="H31">
+      <c r="I31">
         <v>57.90861</v>
-      </c>
-      <c r="I31">
-        <v>42.17926</v>
       </c>
     </row>
     <row r="32">
@@ -1338,28 +1338,28 @@
         </is>
       </c>
       <c r="B32">
+        <v>55.93803</v>
+      </c>
+      <c r="C32">
+        <v>97.55813999999999</v>
+      </c>
+      <c r="D32">
+        <v>84.35643</v>
+      </c>
+      <c r="E32">
+        <v>33.36624</v>
+      </c>
+      <c r="F32">
         <v>55.93804</v>
       </c>
-      <c r="C32">
-        <v>55.93803</v>
-      </c>
-      <c r="D32">
+      <c r="G32">
         <v>102.3256</v>
       </c>
-      <c r="E32">
-        <v>97.55813999999999</v>
-      </c>
-      <c r="F32">
+      <c r="H32">
         <v>110.8911</v>
       </c>
-      <c r="G32">
-        <v>84.35643</v>
-      </c>
-      <c r="H32">
+      <c r="I32">
         <v>47.68016</v>
-      </c>
-      <c r="I32">
-        <v>33.36624</v>
       </c>
     </row>
     <row r="33">
@@ -1372,25 +1372,25 @@
         <v>52.77778</v>
       </c>
       <c r="C33">
+        <v>98.26990000000001</v>
+      </c>
+      <c r="D33">
+        <v>92.81046000000001</v>
+      </c>
+      <c r="E33">
+        <v>37.14286</v>
+      </c>
+      <c r="F33">
         <v>52.77778</v>
       </c>
-      <c r="D33">
+      <c r="G33">
         <v>99.30795999999999</v>
       </c>
-      <c r="E33">
-        <v>98.26990000000001</v>
-      </c>
-      <c r="F33">
+      <c r="H33">
         <v>107.8431</v>
       </c>
-      <c r="G33">
-        <v>92.81046000000001</v>
-      </c>
-      <c r="H33">
+      <c r="I33">
         <v>46.66667</v>
-      </c>
-      <c r="I33">
-        <v>37.14286</v>
       </c>
     </row>
     <row r="34">
@@ -1400,28 +1400,28 @@
         </is>
       </c>
       <c r="B34">
+        <v>63.81119</v>
+      </c>
+      <c r="C34">
+        <v>95.79707000000001</v>
+      </c>
+      <c r="D34">
+        <v>86.18232999999999</v>
+      </c>
+      <c r="E34">
+        <v>38.07711</v>
+      </c>
+      <c r="F34">
         <v>64.16083999999999</v>
       </c>
-      <c r="C34">
-        <v>63.81119</v>
-      </c>
-      <c r="D34">
+      <c r="G34">
         <v>100.4228</v>
       </c>
-      <c r="E34">
-        <v>95.79707000000001</v>
-      </c>
-      <c r="F34">
+      <c r="H34">
         <v>105.4131</v>
       </c>
-      <c r="G34">
-        <v>86.18232999999999</v>
-      </c>
-      <c r="H34">
+      <c r="I34">
         <v>51.85626</v>
-      </c>
-      <c r="I34">
-        <v>38.07711</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:37</t>
+    <t xml:space="preserve">2026-08-02 19:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:39</t>
+    <t xml:space="preserve">2026-08-05 10:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:31</t>
+    <t xml:space="preserve">2026-08-05 18:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 18:12</t>
+    <t xml:space="preserve">2026-08-16 09:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:43</t>
+    <t xml:space="preserve">2026-08-19 11:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:38</t>
+    <t xml:space="preserve">2026-08-28 11:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:20</t>
+    <t xml:space="preserve">2026-09-06 17:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
